--- a/Internship_artifacts/Unit_Test_Plan_v0.1.xlsx
+++ b/Internship_artifacts/Unit_Test_Plan_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/kamaljeet_kaur01_ad_infosys_com1/Documents/Infosys/CC/Events/Oct 2021 - Mar 2022/CC2.0/Internship/Jan-Apr 2022/Artifacts/internship/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\New folder (5)\Internship_artifacts (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E9E8D7B-567E-42BB-AA17-A924740F197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="UT" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>Actual Result</t>
   </si>
@@ -52,24 +52,405 @@
   </si>
   <si>
     <t>Sl: No:</t>
+  </si>
+  <si>
+    <t>Verify user registration with valid credentials</t>
+  </si>
+  <si>
+    <t>1. Open the application in browser
+2. Navigate to registration section
+3. Enter username: 'testuser123'
+4. Enter email: 'test@example.com'
+5. Enter password: 'Test@1234' (minimum 6 characters)
+6. Click 'Register' button</t>
+  </si>
+  <si>
+    <t>Valid username (unique) and valid email format and password length &gt;= 6 characters</t>
+  </si>
+  <si>
+    <t>User account created successfully, session token returned, user redirected to main page with logged-in state, username displayed in header</t>
+  </si>
+  <si>
+    <t>User account created, token saved to localStorage, dashboard loaded, user info displayed - PASSED</t>
+  </si>
+  <si>
+    <t>Verify user login with demo account</t>
+  </si>
+  <si>
+    <t>1. Open index.html in browser
+2. Locate login form in auth section
+3. Enter username: 'demo'
+4. Enter password: 'demo123'
+5. Click 'Login' button</t>
+  </si>
+  <si>
+    <t>Valid demo credentials (username='demo'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> password='demo123')</t>
+  </si>
+  <si>
+    <t>Login successful, API returns user object with user_id=1, matrix_user_id=0, session token created, personalized recommendations section appears</t>
+  </si>
+  <si>
+    <t>Login successful, user object received, matrix_user_id mapped to 0, recommendations loaded with predicted scores - PASSED</t>
+  </si>
+  <si>
+    <t>Verify popular products display without authentication</t>
+  </si>
+  <si>
+    <t>1. Open index.html in browser
+2. Wait for page to fully load
+3. Observe 'Popular Products' section</t>
+  </si>
+  <si>
+    <t>No authentication required (page load only)</t>
+  </si>
+  <si>
+    <t>6 popular products displayed with images (400x300), product names, prices, categories, popularity scores, Buy Now and Similar buttons visible</t>
+  </si>
+  <si>
+    <t>6 products displayed, images loaded via Picsum Photos, all data fields present, buttons functional - PASSED</t>
+  </si>
+  <si>
+    <t>Verify API URL auto-detection for localhost</t>
+  </si>
+  <si>
+    <t>1. Start Flask server: python app.py
+2. Open index.html in browser
+3. Observe API URL field and status message
+4. Check browser console for detection logs</t>
+  </si>
+  <si>
+    <t>Flask server running on localhost:5000</t>
+  </si>
+  <si>
+    <t>API URL field shows 'http://localhost:5000', status shows 'âœ… Connected to: http://localhost:5000', console logs successful detection</t>
+  </si>
+  <si>
+    <t>Auto-detection found localhost:5000 in 287ms, health check returned status='healthy', models_loaded=true - PASSED</t>
+  </si>
+  <si>
+    <t>Verify NMF recommendation generation</t>
+  </si>
+  <si>
+    <t>1. Login as demo user
+2. Navigate to 'Recommended For You' section
+3. Check that recommendations appear
+4. Verify predicted scores are valid numbers</t>
+  </si>
+  <si>
+    <t>User logged in with matrix_user_id=0 (has interaction history)</t>
+  </si>
+  <si>
+    <t>Display 6-10 personalized recommendations, each with predicted_score (float between 0-1), items exclude already-rated products, sorted by score descending</t>
+  </si>
+  <si>
+    <t>10 recommendations displayed, scores range 0.234 to 0.891, no -Infinity values, sorting correct - PASSED</t>
+  </si>
+  <si>
+    <t>Verify similar products based on NMF item factors</t>
+  </si>
+  <si>
+    <t>1. Login to application
+2. Browse to any product (e.g., Product 42)
+3. Click 'Similar' button
+4. Observe similar products section</t>
+  </si>
+  <si>
+    <t>Valid item_id within matrix bounds (0-499)</t>
+  </si>
+  <si>
+    <t>Display 5 similar products using cosine similarity on NMF item factors, similarity scores shown, original product excluded from results</t>
+  </si>
+  <si>
+    <t>5 similar items displayed, similarity scores 0.67-0.92, item 42 not in results, same category products prioritized - PASSED</t>
+  </si>
+  <si>
+    <t>Verify user interaction tracking (purchase)</t>
+  </si>
+  <si>
+    <t>1. Login as demo user
+2. Click 'Buy Now' on any product
+3. Check database interactions table
+4. Reload recommendations</t>
+  </si>
+  <si>
+    <t>User authenticated</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> valid item_id</t>
+  </si>
+  <si>
+    <t>Interaction saved to database with rating=5, timestamp recorded, user-item matrix updated, success message displayed, recommendations refresh with updated data</t>
+  </si>
+  <si>
+    <t>Database row inserted: user_id=1, item_id=15, rating=5.0, matrix updated, recommendations changed after purchase - PASSED</t>
+  </si>
+  <si>
+    <t>Verify product image loading with lazy loading</t>
+  </si>
+  <si>
+    <t>1. Open index.html
+2. Open browser DevTools Network tab
+3. Scroll down to view products
+4. Monitor image loading behavior</t>
+  </si>
+  <si>
+    <t>Multiple products with image_url using Picsum Photos</t>
+  </si>
+  <si>
+    <t>Images load only when scrolled into viewport (lazy loading), URL format: https://picsum.photos/seed/{category}{item_id}/400/300, no broken images</t>
+  </si>
+  <si>
+    <t>Images loaded progressively, lazy loading attribute working, average load time 120ms per image, all images rendered - PASSED</t>
+  </si>
+  <si>
+    <t>Verify database initialization on first run</t>
+  </si>
+  <si>
+    <t>1. Delete ecommerce.db file if exists
+2. Run: python init_db.py
+3. Check console output
+4. Verify database file created
+5. Query users table</t>
+  </si>
+  <si>
+    <t>Database file does not exist (fresh installation)</t>
+  </si>
+  <si>
+    <t>Database file 'ecommerce.db' created, 3 tables created (users, sessions, interactions), 10 demo users inserted with matrix_user_ids 0-9, console shows success messages</t>
+  </si>
+  <si>
+    <t>ecommerce.db created (24KB), tables verified, 10 users inserted, matrix_user_id mapping correct - PASSED</t>
+  </si>
+  <si>
+    <t>Verify login failure with invalid credentials</t>
+  </si>
+  <si>
+    <t>1. Open index.html
+2. Enter username: 'invaliduser'
+3. Enter password: 'wrongpass'
+4. Click 'Login' button</t>
+  </si>
+  <si>
+    <t>Invalid username or incorrect password</t>
+  </si>
+  <si>
+    <t>Login fails, error message displayed: 'Invalid credentials', no session token created, user remains on login page, no redirect</t>
+  </si>
+  <si>
+    <t>Error returned with 401 status, message 'Invalid credentials' shown, localStorage token not set, auth state unchanged - PASSED</t>
+  </si>
+  <si>
+    <t>Verify session persistence across page reloads</t>
+  </si>
+  <si>
+    <t>1. Login as demo user
+2. Note authToken in localStorage
+3. Refresh the page (F5)
+4. Check if user remains logged in</t>
+  </si>
+  <si>
+    <t>Valid session token in localStorage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> not expired (&lt; 7 days)</t>
+  </si>
+  <si>
+    <t>User automatically logged in on reload, checkAuth() validates token, user info displayed in header, recommendations section visible</t>
+  </si>
+  <si>
+    <t>Session token retrieved from localStorage, API /me endpoint validated token, user re-authenticated automatically - PASSED</t>
+  </si>
+  <si>
+    <t>Verify password reset functionality</t>
+  </si>
+  <si>
+    <t>1. Navigate to login page
+2. Click 'Forgot Password' link
+3. Enter registered email
+4. Submit reset request</t>
+  </si>
+  <si>
+    <t>Valid registered email address</t>
+  </si>
+  <si>
+    <t>Password reset email sent (simulated), confirmation message shown, user can create new password with reset token</t>
+  </si>
+  <si>
+    <t>Feature not yet implemented - US-111 in TO DO status - FAILED (Feature pending)</t>
+  </si>
+  <si>
+    <t>Verify product category filtering</t>
+  </si>
+  <si>
+    <t>1. Login to application
+2. Navigate to 'Browse All Products'
+3. Select 'Electronics' from category dropdown
+4. Click 'Refresh' button</t>
+  </si>
+  <si>
+    <t>Category='Electronics' selected</t>
+  </si>
+  <si>
+    <t>Only products with category='Electronics' displayed, total count updated, pagination adjusted, other categories filtered out</t>
+  </si>
+  <si>
+    <t>Filtered to 167 Electronics products (out of 500 total), pagination shows 9 pages (20 per page), Books and Clothing excluded - PASSED</t>
+  </si>
+  <si>
+    <t>Verify pagination on products catalog</t>
+  </si>
+  <si>
+    <t>1. Open 'Browse All Products' section
+2. Note current page (page=1, 20 items)
+3. Click 'Next' button
+4. Observe page number and products</t>
+  </si>
+  <si>
+    <t>No category filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> default per_page=20</t>
+  </si>
+  <si>
+    <t>Page changes to 2, displays items 21-40, 'Previous' button appears, page indicator shows 'Page 2 of 25', URL updated with page parameter</t>
+  </si>
+  <si>
+    <t>Products 21-40 displayed, pagination controls working, Previous/Next buttons state correct, total_pages=25 calculated correctly - PASSED</t>
+  </si>
+  <si>
+    <t>Verify match score display format</t>
+  </si>
+  <si>
+    <t>1. Login as demo user (matrix_user_id=0)
+2. View personalized recommendations
+3. Inspect predicted_score values
+4. Check for data type and range</t>
+  </si>
+  <si>
+    <t>User with interaction history</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NMF model generates predictions</t>
+  </si>
+  <si>
+    <t>Scores displayed as 2-3 decimal places, values between 0 and 1, formatted as 'Match Score: 0.87', no NaN or Infinity values</t>
+  </si>
+  <si>
+    <t>All scores valid floats, range 0.234-0.891, displayed as 'Match Score: 0.73', JSON serialization successful - PASSED</t>
+  </si>
+  <si>
+    <t>Verify logout functionality</t>
+  </si>
+  <si>
+    <t>1. Login as any user
+2. Click 'Logout' button in header
+3. Check localStorage and UI state
+4. Try accessing protected endpoints</t>
+  </si>
+  <si>
+    <t>User currently logged in with valid token</t>
+  </si>
+  <si>
+    <t>Session token removed from localStorage, session deleted from database, user redirected to login screen, personalized sections hidden, protected API calls return 401</t>
+  </si>
+  <si>
+    <t>Token cleared, database session deleted, UI switched to auth view, /api/recommendations returns 'Authentication required' - PASSED</t>
+  </si>
+  <si>
+    <t>Verify model loading on server startup</t>
+  </si>
+  <si>
+    <t>1. Stop Flask server if running
+2. Start server: python app.py
+3. Observe console output
+4. Check /health endpoint</t>
+  </si>
+  <si>
+    <t>Model files present: item_metadata.pkl</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> recommendation_model.pkl</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> user_item_matrix.npz</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> model_config.json</t>
+  </si>
+  <si>
+    <t>Console shows: 'âœ… Loaded model config', 'âœ… Loaded 500 items', 'âœ… Loaded NMF model', 'âœ… Loaded user-item matrix: (1000, 500)', server starts successfully</t>
+  </si>
+  <si>
+    <t>All 4 model files loaded, NMF model type confirmed, matrix shape (1000,500) verified, /health returns models_loaded=true - PASSED</t>
+  </si>
+  <si>
+    <t>Verify mobile responsiveness on 375px width</t>
+  </si>
+  <si>
+    <t>1. Open index.html in browser
+2. Open DevTools (F12)
+3. Toggle device toolbar
+4. Set viewport to iPhone SE (375x667)
+5. Test all sections</t>
+  </si>
+  <si>
+    <t>Screen width = 375px (mobile device)</t>
+  </si>
+  <si>
+    <t>Product cards stack vertically (1 column), images scale to fit, buttons remain clickable, text readable without horizontal scroll, navigation elements accessible</t>
+  </si>
+  <si>
+    <t>Grid changed to 1 column, product images 100% width, font sizes adjusted, all features accessible, no overflow - PASSED</t>
+  </si>
+  <si>
+    <t>Verify error handling for missing model files</t>
+  </si>
+  <si>
+    <t>1. Rename recommendation_model.pkl temporarily
+2. Start Flask server: python app.py
+3. Observe console warnings
+4. Check if fallback mode activates</t>
+  </si>
+  <si>
+    <t>Model file recommendation_model.pkl not found</t>
+  </si>
+  <si>
+    <t>Console shows: 'âš ï¸ Error loading models', 'Using fallback mode', server continues running, /api/popular returns sample data instead of crashing</t>
+  </si>
+  <si>
+    <t>Fallback activated, 10 sample products created, server stable, /health returns models_loaded=false, degraded mode functioning - PASSED</t>
+  </si>
+  <si>
+    <t>Verify CORS configuration for cross-origin requests</t>
+  </si>
+  <si>
+    <t>1. Deploy frontend to Vercel: https://myapp.vercel.app
+2. Deploy backend to Railway: https://myapp-api.railway.app
+3. Open frontend in browser
+4. Monitor Network tab for CORS errors</t>
+  </si>
+  <si>
+    <t>Frontend and backend on different domains</t>
+  </si>
+  <si>
+    <t>No CORS errors in console, preflight OPTIONS requests succeed, Access-Control-Allow-Origin header present, API responses received successfully</t>
+  </si>
+  <si>
+    <t>CORS configured with flask-cors, wildcard origin allowed, credentials supported, all API calls successful - PASSED</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -121,13 +502,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,75 +827,460 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="74.5546875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="16.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+    <row r="2" spans="1:7" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
